--- a/docs/統計檢定結果.xlsx
+++ b/docs/統計檢定結果.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -613,24 +613,24 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.98E-08</t>
+          <t>2.69E-05</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.7686195028650199</v>
+        <v>0.5821426524987382</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.99982</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0.00018</v>
       </c>
     </row>
     <row r="7">
@@ -644,44 +644,48 @@
           <t>程式編排 vs 手動編排</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NaN</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t>2.98E-08</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.7686195028650199</v>
+      </c>
       <c r="F7" t="n">
-        <v>0.03448275862068965</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03448275862068965</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9310344827586207</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>Hierarchical Objective</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>程式編排 vs 手動編排</t>
+          <t>程式編排 vs 程式(alb_extract)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.98E-08</t>
+          <t>9.83E-07</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.7686195028650199</v>
+        <v>0.6788027340424763</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
@@ -696,7 +700,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Hierarchical Objective</t>
+          <t>NV</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -705,15 +709,15 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>9.83E-07</t>
+          <t>2.62E-06</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.6788027340424763</v>
+        <v>0.6515451337233447</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
@@ -728,7 +732,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NV</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -737,7 +741,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -760,7 +764,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -769,15 +773,15 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.62E-06</t>
+          <t>2.98E-08</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.6515451337233447</v>
+        <v>0.7686195028650199</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -792,7 +796,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>U</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -801,15 +805,15 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.98E-08</t>
+          <t>5.66E-07</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.7686195028650199</v>
+        <v>0.6937064331520529</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
@@ -824,7 +828,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -833,15 +837,15 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>7.65E-05</t>
+          <t>7.45E-07</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.5484905304567255</v>
+        <v>0.686335384152069</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
@@ -856,71 +860,71 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>Hierarchical Objective</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>程式編排 vs 程式(alb_extract)</t>
+          <t>程式編排 vs 程式(alb_allocate)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>9.5</v>
+        <v>145</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.62E-04</t>
+          <t>4.52E-01</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.5229763603684919</v>
+        <v>0.104186477066251</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0.78242</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>0.21758</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>NV</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>程式編排 vs 程式(alb_extract)</t>
+          <t>程式編排 vs 程式(alb_allocate)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>148</v>
+        <v>124.5</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4.99E-01</t>
+          <t>4.66E-01</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.09371061338620754</v>
+        <v>0.10107594250783</v>
       </c>
       <c r="F15" t="n">
-        <v>0.25022</v>
+        <v>0.76104</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.74978</v>
+        <v>0.23896</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Hierarchical Objective</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -929,30 +933,30 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>145</v>
+        <v>125.5</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>4.52E-01</t>
+          <t>4.84E-01</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.104186477066251</v>
+        <v>0.09708244121644653</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7846</v>
+        <v>0.7544</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2154</v>
+        <v>0.2456</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NV</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -961,30 +965,30 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>124.5</v>
+        <v>81</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>4.66E-01</t>
+          <t>1.51E-02</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.10107594250783</v>
+        <v>0.3368696057008946</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7630400000000001</v>
+        <v>0.99468</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.23696</v>
+        <v>0.00532</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>U</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -993,30 +997,30 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>125.5</v>
+        <v>129.5</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>4.84E-01</t>
+          <t>3.75E-01</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.09708244121644653</v>
+        <v>0.1231390432007663</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7537</v>
+        <v>0.8151</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2463</v>
+        <v>0.1849</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1025,126 +1029,126 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.51E-02</t>
+          <t>4.97E-01</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.3368696057008946</v>
+        <v>0.09415402031965983</v>
       </c>
       <c r="F19" t="n">
-        <v>0.99494</v>
+        <v>0.33296</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.00506</v>
+        <v>0.66704</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>Hierarchical Objective</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>程式編排 vs 程式(alb_allocate)</t>
+          <t>程式編排 vs 程式(alb_support)</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.57E-01</t>
+          <t>2.93E-03</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.1572427255082877</v>
+        <v>0.4125140010719477</v>
       </c>
       <c r="F20" t="n">
-        <v>0.88822</v>
+        <v>0.99938</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.11178</v>
+        <v>0.00062</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>NV</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>程式編排 vs 程式(alb_allocate)</t>
+          <t>程式編排 vs 程式(alb_support)</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3.17E-01</t>
+          <t>5.72E-03</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.1386750490563073</v>
+        <v>0.3832204322446793</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>0.99876</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>0.00124</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>程式編排 vs 程式(alb_allocate)</t>
+          <t>程式編排 vs 程式(alb_support)</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.66E-04</t>
+          <t>5.72E-03</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.5221888968568675</v>
+        <v>0.3832204322446793</v>
       </c>
       <c r="F22" t="n">
-        <v>4e-05</v>
+        <v>0.99884</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.99996</v>
+        <v>0.00116</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Hierarchical Objective</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1153,30 +1157,30 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2.93E-03</t>
+          <t>1.30E-03</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.4125140010719477</v>
+        <v>0.4460380174419469</v>
       </c>
       <c r="F23" t="n">
-        <v>0.99942</v>
+        <v>0.9998</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.00058</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NV</t>
+          <t>U</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1185,30 +1189,30 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>5.72E-03</t>
+          <t>8.72E-05</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.3832204322446793</v>
+        <v>0.5441270326046462</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9987200000000001</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.00128</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1217,67 +1221,67 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>36</v>
+        <v>98.5</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>5.72E-03</t>
+          <t>3.62E-01</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.3832204322446793</v>
+        <v>0.1263609443090515</v>
       </c>
       <c r="F25" t="n">
-        <v>0.99878</v>
+        <v>0.23774</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.00122</v>
+        <v>0.76226</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Hierarchical Objective</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>程式編排 vs 程式(alb_support)</t>
+          <t>程式編排 vs 程式(alb_single_stage_ga)</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.30E-03</t>
+          <t>2.98E-08</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.4460380174419469</v>
+        <v>0.7686195028650199</v>
       </c>
       <c r="F26" t="n">
-        <v>0.99978</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.00022</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>NV</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>程式編排 vs 程式(alb_support)</t>
+          <t>程式編排 vs 程式(alb_single_stage_ga)</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1285,11 +1289,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.41E-02</t>
+          <t>2.98E-08</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.3405529787873641</v>
+        <v>0.7686195028650199</v>
       </c>
       <c r="F27" t="n">
         <v>1</v>
@@ -1304,12 +1308,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>程式編排 vs 程式(alb_support)</t>
+          <t>程式編排 vs 程式(alb_single_stage_ga)</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1317,31 +1321,31 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.57E-01</t>
+          <t>2.98E-08</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.1961161351381841</v>
+        <v>0.7686195028650199</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>程式編排 vs 程式(alb_support)</t>
+          <t>程式編排 vs 程式(alb_single_stage_ga)</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1356,13 +1360,77 @@
         <v>0.7686195028650199</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>程式編排 vs 程式(alb_single_stage_ga)</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2.98E-08</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0.7686195028650199</v>
+      </c>
+      <c r="F30" t="n">
         <v>1</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>程式編排 vs 程式(alb_single_stage_ga)</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>6</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>4.17E-07</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0.7018236939263505</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1376,7 +1444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1412,7 +1480,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>RT Rank</t>
+          <t>O Rank</t>
         </is>
       </c>
     </row>
@@ -1423,22 +1491,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.92</v>
+        <v>5.58</v>
       </c>
       <c r="C2" t="n">
-        <v>4.87</v>
+        <v>5.52</v>
       </c>
       <c r="D2" t="n">
-        <v>4.9</v>
+        <v>5.63</v>
       </c>
       <c r="E2" t="n">
-        <v>3.85</v>
+        <v>4.08</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>5.35</v>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -1460,10 +1528,10 @@
         <v>1.65</v>
       </c>
       <c r="F3" t="n">
-        <v>2.92</v>
+        <v>1.77</v>
       </c>
       <c r="G3" t="n">
-        <v>3.38</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="4">
@@ -1473,22 +1541,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.62</v>
+        <v>3.69</v>
       </c>
       <c r="C4" t="n">
-        <v>3.6</v>
+        <v>3.69</v>
       </c>
       <c r="D4" t="n">
-        <v>3.56</v>
+        <v>3.65</v>
       </c>
       <c r="E4" t="n">
-        <v>4.73</v>
+        <v>4.96</v>
       </c>
       <c r="F4" t="n">
-        <v>4.5</v>
+        <v>3.77</v>
       </c>
       <c r="G4" t="n">
-        <v>3.38</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -1510,10 +1578,10 @@
         <v>2.19</v>
       </c>
       <c r="F5" t="n">
-        <v>3.15</v>
+        <v>2.02</v>
       </c>
       <c r="G5" t="n">
-        <v>2.23</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="6">
@@ -1535,71 +1603,96 @@
         <v>2.58</v>
       </c>
       <c r="F6" t="n">
-        <v>3.42</v>
+        <v>2.75</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Friedman Statistic</t>
+          <t>程式(alb_single_stage_ga)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>67.54000000000001</v>
+        <v>5.27</v>
       </c>
       <c r="C7" t="n">
-        <v>65.97</v>
+        <v>5.25</v>
       </c>
       <c r="D7" t="n">
-        <v>67.06</v>
+        <v>5.17</v>
       </c>
       <c r="E7" t="n">
-        <v>66.09</v>
+        <v>5.54</v>
       </c>
       <c r="F7" t="n">
-        <v>79.73999999999999</v>
+        <v>5.35</v>
       </c>
       <c r="G7" t="n">
-        <v>92.43000000000001</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Friedman Statistic</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>97.95999999999999</v>
+      </c>
+      <c r="C8" t="n">
+        <v>96.23999999999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>97.78</v>
+      </c>
+      <c r="E8" t="n">
+        <v>93.56</v>
+      </c>
+      <c r="F8" t="n">
+        <v>94.62</v>
+      </c>
+      <c r="G8" t="n">
+        <v>104.82</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>p-value</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>7.51E-14</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1.61E-13</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>9.47E-14</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>1.51E-13</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>1.97E-16</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>4.01E-19</t>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1.42E-19</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3.27E-19</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1.55E-19</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1.20E-18</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>7.17E-19</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>5.09E-21</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1653,11 +1746,6 @@
           <t>O Rank</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>RT Rank</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1678,13 +1766,10 @@
         <v>1.54</v>
       </c>
       <c r="F2" t="n">
-        <v>1.92</v>
+        <v>1.73</v>
       </c>
       <c r="G2" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="H2" t="n">
-        <v>3.38</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="3">
@@ -1694,25 +1779,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.54</v>
+        <v>3.62</v>
       </c>
       <c r="C3" t="n">
-        <v>3.52</v>
+        <v>3.62</v>
       </c>
       <c r="D3" t="n">
-        <v>3.52</v>
+        <v>3.62</v>
       </c>
       <c r="E3" t="n">
-        <v>3.96</v>
+        <v>4.19</v>
       </c>
       <c r="F3" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="G3" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="H3" t="n">
-        <v>3.38</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -1734,13 +1816,10 @@
         <v>2.12</v>
       </c>
       <c r="F4" t="n">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="G4" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2.23</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="5">
@@ -1762,82 +1841,96 @@
         <v>2.38</v>
       </c>
       <c r="F5" t="n">
-        <v>2.42</v>
+        <v>2.71</v>
       </c>
       <c r="G5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Friedman Statistic</t>
+          <t>程式(alb_single_stage_ga)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26.63</v>
+        <v>4.92</v>
       </c>
       <c r="C6" t="n">
-        <v>26.68</v>
+        <v>4.9</v>
       </c>
       <c r="D6" t="n">
-        <v>26.68</v>
+        <v>4.9</v>
       </c>
       <c r="E6" t="n">
-        <v>50.26</v>
+        <v>4.77</v>
       </c>
       <c r="F6" t="n">
-        <v>33.24</v>
+        <v>4.92</v>
       </c>
       <c r="G6" t="n">
-        <v>43.03</v>
-      </c>
-      <c r="H6" t="n">
-        <v>60.65</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Friedman Statistic</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>67.54000000000001</v>
+      </c>
+      <c r="C7" t="n">
+        <v>68.15000000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>68.15000000000001</v>
+      </c>
+      <c r="E7" t="n">
+        <v>81.63</v>
+      </c>
+      <c r="F7" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>68.11</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>p-value</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>7.04E-06</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>6.87E-06</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>6.87E-06</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>7.03E-11</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2.87E-07</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2.42E-09</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>4.28E-13</t>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>7.51E-14</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>5.57E-14</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>5.57E-14</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>7.86E-17</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>7.40E-15</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>5.68E-14</t>
         </is>
       </c>
     </row>
@@ -1852,7 +1945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1891,11 +1984,6 @@
           <t>O Rank</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>RT Rank</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1916,13 +2004,10 @@
         <v>1.54</v>
       </c>
       <c r="F2" t="n">
-        <v>1.92</v>
+        <v>1.73</v>
       </c>
       <c r="G2" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="H2" t="n">
-        <v>3.38</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="3">
@@ -1944,13 +2029,10 @@
         <v>3.96</v>
       </c>
       <c r="F3" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="G3" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="H3" t="n">
-        <v>3.38</v>
+        <v>3.81</v>
       </c>
     </row>
     <row r="4">
@@ -1972,13 +2054,10 @@
         <v>2.12</v>
       </c>
       <c r="F4" t="n">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="G4" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2.23</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="5">
@@ -2000,13 +2079,10 @@
         <v>2.38</v>
       </c>
       <c r="F5" t="n">
-        <v>2.42</v>
+        <v>2.71</v>
       </c>
       <c r="G5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="6">
@@ -2028,13 +2104,10 @@
         <v>50.26</v>
       </c>
       <c r="F6" t="n">
-        <v>33.24</v>
+        <v>33.12</v>
       </c>
       <c r="G6" t="n">
-        <v>43.03</v>
-      </c>
-      <c r="H6" t="n">
-        <v>60.65</v>
+        <v>38.77</v>
       </c>
     </row>
     <row r="7">
@@ -2065,17 +2138,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2.87E-07</t>
+          <t>3.04E-07</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2.42E-09</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>4.28E-13</t>
+          <t>1.94E-08</t>
         </is>
       </c>
     </row>
